--- a/execution/fixtures/inputs/Gorlocks-2026-05-21-10-00-00.xlsx
+++ b/execution/fixtures/inputs/Gorlocks-2026-05-21-10-00-00.xlsx
@@ -397,19 +397,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A18:K29"/>
+  <dimension ref="A2:K29"/>
   <sheetData>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>2026-27 Active YJ - 1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>As of 2026-05-21 10:00:00 MST</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Filtered By</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>Yellow Jacket Credit- Opportunities</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>Show: All accounts</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Date Field: Opportunity: Close Date equals Custom (1/1/2026 to 12/31/2026)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Account Name contains Yellow Jacket</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Yellow Jacket Team equals Gorlocks</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Volunteer Points</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Show: All accounts</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Date Field: Planned Start Date &amp; Time equals Custom (1/1/2026 to 12/31/2026)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Account Name contains Yellow Jacket</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Yellow Jacket Team equals Gorlocks</v>
+      </c>
+    </row>
     <row r="18">
       <c r="B18" t="str">
-        <v>Yellow Jacket Team equals Gorlocks</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="str">
         <v>Contacts with Custom Object</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G18" t="str">
         <v>Contacts with Custom Object</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Yellow Jacket Credit- Opportunities</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Volunteer Points</v>
       </c>
     </row>
     <row r="21">
@@ -556,7 +624,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A18:K29"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:K29"/>
   </ignoredErrors>
 </worksheet>
 </file>